--- a/docs/economics/browser-fleet-economics.xlsx
+++ b/docs/economics/browser-fleet-economics.xlsx
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>1</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>249</v>
+        <v>179</v>
       </c>
       <c r="C6" s="15" t="n">
         <v>3</v>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>699</v>
+        <v>499</v>
       </c>
       <c r="C7" s="15" t="n">
         <v>10</v>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>1500</v>
+        <v>998</v>
       </c>
       <c r="C8" s="18">
         <f>'1_Assumptions'!$B$27</f>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Fair-Use Cap aus Assumptions. Preis-Floor 1500 (ADR-001).</t>
+          <t>Fair-Use Cap aus Assumptions. Preis-Floor 998 (pricing.ts).</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>EUR 79 mit 1 Domain + monatlichem Re-Scan ist enges Sweet-Spot. Stripe + Cost-per-Scan duerfen nicht &gt; 25% des Tier-Preises kommen. Sheet 2 Zelle H5 wachhalten.</t>
+          <t>EUR 49 mit 1 Domain + monatlichem Re-Scan ist nach dem Rebalance vom 18.05. enges Sweet-Spot. Stripe + Cost-per-Scan duerfen nicht &gt; 25% des Tier-Preises kommen. Sheet 2 Zelle H5 wachhalten.</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>EUR 249 mit 3 Domains taeglich ist das Tier mit hoechster absoluter Marge. Sales-Fokus: Starter -&gt; Growth-Upgrade nach 30 Tagen.</t>
+          <t>EUR 179 mit 3 Domains taeglich ist das Tier mit hoechster absoluter Marge. Sales-Fokus: Starter -&gt; Growth-Upgrade nach 30 Tagen.</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>EUR 699 fuer 10 Kundenseiten. Wenn ein Agency-Kunde via API &gt; 10 Domains pushed, automatische Quota-Warnung. Overage-Pricing oder Upgrade-Flow.</t>
+          <t>EUR 499 fuer 10 Kundenseiten. Wenn ein Agency-Kunde via API &gt; 10 Domains pushed, automatische Quota-Warnung. Overage-Pricing oder Upgrade-Flow.</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>Bei EUR 79 / 249 sind 1.4% + 0.25 EUR Karten-Fee schmerzhaft. SEPA Direct Debit: 0.8% + 0.25 EUR. Margen-Effekt auf Starter sichtbar in Sheet 2.</t>
+          <t>Bei EUR 49 / 179 sind 1.4% + 0.25 EUR Karten-Fee schmerzhaft (besonders fuer Starter). SEPA Direct Debit: 0.8% + 0.25 EUR. Margen-Effekt auf Starter sichtbar in Sheet 2.</t>
         </is>
       </c>
     </row>
